--- a/output/2026-10-02_16_Malesia_Negeri_Sembilan_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-02_16_Malesia_Negeri_Sembilan_Impiantistica_aspirazione_industriale.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Produttore/integratore sistemi aspirazione polveri (filtri, ventilatori, condotte) per legno, agro-milling, riciclo, metalworking, carta. Verificato via sito ufficiale e dustcollector.com.my. N. reg. 199501014828/344029-K.</t>
+          <t>Produttore/integratore sistemi aspirazione polveri (filtri, ventilatori, condotte) per legno, agro-milling, riciclo, metalworking, carta. Verificato via sito ufficiale e dustcollector.com.my. N. reg. 199501014828/344029-K. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fornitore sistemi controllo inquinamento aria, dust collector, vacuum centralizzato. ATTENZIONE: sede legale in Selangor, non in Negeri Sembilan - copertura NS dichiarata ma non verificata con sede fisica in loco. N. reg. 199501003336/332530-K.</t>
+          <t>Fornitore sistemi controllo inquinamento aria, dust collector, vacuum centralizzato. ATTENZIONE: sede legale in Selangor, non in Negeri Sembilan - copertura NS dichiarata ma non verificata con sede fisica in loco. N. reg. 199501003336/332530-K. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>"Ventilation Architect" - progettazione/installazione ventilazione, LEV, cappe fumi, scrubber. System integrator B2B, status Bumiputera. Core-fit per il settore. Verificato via sito ufficiale.</t>
+          <t>"Ventilation Architect" - progettazione/installazione ventilazione, LEV, cappe fumi, scrubber. System integrator B2B, status Bumiputera. Core-fit per il settore. Verificato via sito ufficiale. [DUPLICATO — vedi anche: 2026-10-02_15_Malesia_Negeri_Sembilan_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rivenditore multi-brand (Bosch, Makita, Dewalt, Stihl) di utensili/compressori/pompe/aspiratori industriali - distributore generalista, non specializzato esclusivamente in impiantistica aspirazione ma linea prodotto pertinente confermata. N. reg. 202101043536.</t>
+          <t>Rivenditore multi-brand (Bosch, Makita, Dewalt, Stihl) di utensili/compressori/pompe/aspiratori industriali - distributore generalista, non specializzato esclusivamente in impiantistica aspirazione ma linea prodotto pertinente confermata. N. reg. 202101043536. [DUPLICATO — vedi anche: 2026-10-02_06_Malesia_Negeri_Sembilan_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Agente/distributore Bosch, Makita, Hitachi; vende aspiratori/pressure cleaner (Jetmaster, LAVOR, Tigatan) - distributore generalista hardware/tools, non specializzato in impiantistica pesante. N. reg. 200201008063/575726-V.</t>
+          <t>Agente/distributore Bosch, Makita, Hitachi; vende aspiratori/pressure cleaner (Jetmaster, LAVOR, Tigatan) - distributore generalista hardware/tools, non specializzato in impiantistica pesante. N. reg. 200201008063/575726-V. [DUPLICATO — vedi anche: 2026-10-02_06_Malesia_Negeri_Sembilan_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
